--- a/inst/extdata/Template.xlsx
+++ b/inst/extdata/Template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">TRIAL</t>
   </si>
@@ -30,6 +30,12 @@
   </si>
   <si>
     <t xml:space="preserve">SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
   </si>
   <si>
     <t xml:space="preserve">ROUND_MEAN</t>
@@ -395,6 +401,12 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
